--- a/web/files/港岛-香港仔及鸭脷洲-海盈山第4B期.xlsx
+++ b/web/files/港岛-香港仔及鸭脷洲-海盈山第4B期.xlsx
@@ -3173,7 +3173,7 @@
         </is>
       </c>
       <c r="E39" s="4" t="n">
-        <v>1154</v>
+        <v>1204</v>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
         <v>51534000</v>
       </c>
       <c r="I39" s="5" t="n">
-        <v>44657</v>
+        <v>42802</v>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
@@ -3200,7 +3200,7 @@
         <v>51534000</v>
       </c>
       <c r="L39" s="5" t="n">
-        <v>44657</v>
+        <v>42802</v>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
@@ -3565,38 +3565,30 @@
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H45" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I45" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="H45" s="5" t="n">
+        <v>50472000</v>
+      </c>
+      <c r="I45" s="5" t="n">
+        <v>41920</v>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K45" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L45" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K45" s="5" t="n">
+        <v>50472000</v>
+      </c>
+      <c r="L45" s="5" t="n">
+        <v>41920</v>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
@@ -3605,7 +3597,7 @@
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -4225,7 +4217,7 @@
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G55" s="3" t="inlineStr">
@@ -4235,12 +4227,12 @@
       </c>
       <c r="H55" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I55" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J55" s="3" t="inlineStr">
@@ -4250,12 +4242,12 @@
       </c>
       <c r="K55" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L55" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M55" s="3" t="inlineStr">
@@ -4265,7 +4257,7 @@
       </c>
       <c r="N55" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -12059,34 +12051,34 @@
       </c>
       <c r="F174" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G174" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="H174" s="5" t="n">
-        <v>17109700</v>
+        <v>14030000</v>
       </c>
       <c r="I174" s="5" t="n">
-        <v>35351</v>
+        <v>28988</v>
       </c>
       <c r="J174" s="3" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K174" s="5" t="n">
-        <v>14029954</v>
+        <v>14030000</v>
       </c>
       <c r="L174" s="5" t="n">
         <v>28988</v>
       </c>
       <c r="M174" s="3" t="inlineStr">
         <is>
-          <t>星級 90 天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N174" s="3" t="inlineStr">
@@ -12374,7 +12366,7 @@
       </c>
       <c r="G179" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H179" s="5" t="n">
@@ -13905,23 +13897,23 @@
       </c>
       <c r="F203" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G203" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="H203" s="5" t="n">
-        <v>17100000</v>
+        <v>14022000</v>
       </c>
       <c r="I203" s="5" t="n">
-        <v>34269</v>
+        <v>28100</v>
       </c>
       <c r="J203" s="3" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K203" s="5" t="n">
@@ -13932,7 +13924,7 @@
       </c>
       <c r="M203" s="3" t="inlineStr">
         <is>
-          <t>星級 90 天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N203" s="3" t="inlineStr">
@@ -25567,7 +25559,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -25577,7 +25569,7 @@
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>29</t>
         </is>
       </c>
     </row>
@@ -26028,9 +26020,9 @@
       </c>
       <c r="C23" s="21" t="inlineStr">
         <is>
-          <t>B | 1154呎 (4+房)
+          <t>B | 1204呎 (4+房)
 $5153万
-$44,657/呎
+$42,802/呎
 (26年-06月-05日)</t>
         </is>
       </c>
@@ -26095,12 +26087,12 @@
 (26年-06月-15日)</t>
         </is>
       </c>
-      <c r="C26" s="22" t="inlineStr">
+      <c r="C26" s="21" t="inlineStr">
         <is>
           <t>B | 1204呎 (4+房)
-招标单位
--
-(在售)</t>
+$5047万
+$41,920/呎
+(26年-09月-04日)</t>
         </is>
       </c>
     </row>
@@ -26210,12 +26202,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C31" s="20" t="inlineStr">
+      <c r="C31" s="22" t="inlineStr">
         <is>
           <t>B | 1204呎 (4+房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
     </row>
@@ -26453,7 +26445,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>38</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -26463,7 +26455,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>75</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -27505,12 +27497,12 @@
 (26年-07月-15日)</t>
         </is>
       </c>
-      <c r="E26" s="22" t="inlineStr">
+      <c r="E26" s="21" t="inlineStr">
         <is>
           <t>D | 484呎 (2房)
-$1711万
-$35,351/呎
-(在售)</t>
+$1403万
+$28,988/呎
+(26年-09月-06日)</t>
         </is>
       </c>
       <c r="F26" s="22" t="inlineStr">
@@ -27557,7 +27549,7 @@
           <t>D | 484呎 (2房)
 $1397万
 $28,872/呎
-(26年-08月-10日)</t>
+(26年-09月-04日)</t>
         </is>
       </c>
       <c r="F27" s="22" t="inlineStr">
@@ -27795,12 +27787,12 @@
 (26年-08月-03日)</t>
         </is>
       </c>
-      <c r="F32" s="22" t="inlineStr">
+      <c r="F32" s="21" t="inlineStr">
         <is>
           <t>E | 499呎 (2房)
-$1710万
-$34,269/呎
-(在售)</t>
+$1402万
+$28,100/呎
+(26年-09月-05日)</t>
         </is>
       </c>
     </row>

--- a/web/files/港岛-香港仔及鸭脷洲-海盈山第4B期.xlsx
+++ b/web/files/港岛-香港仔及鸭脷洲-海盈山第4B期.xlsx
@@ -1964,7 +1964,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="H20" s="5" t="n">
@@ -2851,38 +2851,30 @@
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H34" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I34" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="H34" s="5" t="n">
+        <v>73464000</v>
+      </c>
+      <c r="I34" s="5" t="n">
+        <v>48491</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K34" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L34" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K34" s="5" t="n">
+        <v>73464000</v>
+      </c>
+      <c r="L34" s="5" t="n">
+        <v>48491</v>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
@@ -2891,7 +2883,7 @@
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -8164,7 +8156,7 @@
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H112" s="5" t="n">
@@ -11989,34 +11981,34 @@
       </c>
       <c r="F173" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G173" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="H173" s="5" t="n">
-        <v>17513400</v>
+        <v>14361000</v>
       </c>
       <c r="I173" s="5" t="n">
-        <v>35097</v>
+        <v>28780</v>
       </c>
       <c r="J173" s="3" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K173" s="5" t="n">
-        <v>14360988</v>
+        <v>14361000</v>
       </c>
       <c r="L173" s="5" t="n">
         <v>28780</v>
       </c>
       <c r="M173" s="3" t="inlineStr">
         <is>
-          <t>星級 90 天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N173" s="3" t="inlineStr">
@@ -12299,34 +12291,34 @@
       </c>
       <c r="F178" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G178" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="H178" s="5" t="n">
-        <v>17443900</v>
+        <v>14304000</v>
       </c>
       <c r="I178" s="5" t="n">
-        <v>34958</v>
+        <v>28665</v>
       </c>
       <c r="J178" s="3" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K178" s="5" t="n">
-        <v>14303998</v>
+        <v>14304000</v>
       </c>
       <c r="L178" s="5" t="n">
         <v>28665</v>
       </c>
       <c r="M178" s="3" t="inlineStr">
         <is>
-          <t>星級 90 天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N178" s="3" t="inlineStr">
@@ -25549,7 +25541,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -25559,7 +25551,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -25785,7 +25777,7 @@
           <t>A | 1515呎 (4+房)
 $7769万
 $51,280/呎
-(26年-08月-14日)</t>
+(26年-09月-10日)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -25941,12 +25933,12 @@
           <t>27</t>
         </is>
       </c>
-      <c r="B20" s="22" t="inlineStr">
+      <c r="B20" s="21" t="inlineStr">
         <is>
           <t>A | 1515呎 (4+房)
-招标单位
--
-(在售)</t>
+$7346万
+$48,491/呎
+(26年-09月-09日)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -26445,7 +26437,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>36</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -26455,7 +26447,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>77</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -26867,7 +26859,7 @@
           <t>A | 960呎 (3房)
 $4394万
 $45,766/呎
-(26年-08月-21日)</t>
+(26年-09月-09日)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -27505,12 +27497,12 @@
 (26年-09月-06日)</t>
         </is>
       </c>
-      <c r="F26" s="22" t="inlineStr">
+      <c r="F26" s="21" t="inlineStr">
         <is>
           <t>E | 499呎 (2房)
-$1751万
-$35,097/呎
-(在售)</t>
+$1436万
+$28,780/呎
+(26年-09月-08日)</t>
         </is>
       </c>
     </row>
@@ -27552,12 +27544,12 @@
 (26年-09月-04日)</t>
         </is>
       </c>
-      <c r="F27" s="22" t="inlineStr">
+      <c r="F27" s="21" t="inlineStr">
         <is>
           <t>E | 499呎 (2房)
-$1744万
-$34,958/呎
-(在售)</t>
+$1430万
+$28,665/呎
+(26年-09月-10日)</t>
         </is>
       </c>
     </row>

--- a/web/files/港岛-香港仔及鸭脷洲-海盈山第4B期.xlsx
+++ b/web/files/港岛-香港仔及鸭脷洲-海盈山第4B期.xlsx
@@ -2339,38 +2339,30 @@
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H26" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I26" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="H26" s="5" t="n">
+        <v>75396000</v>
+      </c>
+      <c r="I26" s="5" t="n">
+        <v>49766</v>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K26" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L26" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K26" s="5" t="n">
+        <v>75396000</v>
+      </c>
+      <c r="L26" s="5" t="n">
+        <v>49766</v>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
@@ -2379,7 +2371,7 @@
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -4209,38 +4201,30 @@
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H55" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I55" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="H55" s="5" t="n">
+        <v>48118000</v>
+      </c>
+      <c r="I55" s="5" t="n">
+        <v>39965</v>
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K55" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L55" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K55" s="5" t="n">
+        <v>48118000</v>
+      </c>
+      <c r="L55" s="5" t="n">
+        <v>39965</v>
       </c>
       <c r="M55" s="3" t="inlineStr">
         <is>
@@ -4249,7 +4233,7 @@
       </c>
       <c r="N55" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -9903,34 +9887,34 @@
       </c>
       <c r="F140" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="H140" s="5" t="n">
-        <v>20637800</v>
+        <v>16923000</v>
       </c>
       <c r="I140" s="5" t="n">
-        <v>37798</v>
+        <v>30995</v>
       </c>
       <c r="J140" s="3" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K140" s="5" t="n">
-        <v>16922996</v>
+        <v>16923000</v>
       </c>
       <c r="L140" s="5" t="n">
-        <v>30994</v>
+        <v>30995</v>
       </c>
       <c r="M140" s="3" t="inlineStr">
         <is>
-          <t>星級 90 天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N140" s="3" t="inlineStr">
@@ -25541,7 +25525,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -25551,7 +25535,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -25841,12 +25825,12 @@
           <t>31</t>
         </is>
       </c>
-      <c r="B16" s="22" t="inlineStr">
+      <c r="B16" s="21" t="inlineStr">
         <is>
           <t>A | 1515呎 (4+房)
-招标单位
--
-(在售)</t>
+$7540万
+$49,766/呎
+(26年-09月-11日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -26194,12 +26178,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C31" s="22" t="inlineStr">
+      <c r="C31" s="21" t="inlineStr">
         <is>
           <t>B | 1204呎 (4+房)
-招标单位
--
-(在售)</t>
+$4812万
+$39,965/呎
+(26年-09月-11日)</t>
         </is>
       </c>
     </row>
@@ -26437,7 +26421,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>35</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -26447,7 +26431,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>78</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -27152,12 +27136,12 @@
 (26年-07月-23日)</t>
         </is>
       </c>
-      <c r="D19" s="22" t="inlineStr">
+      <c r="D19" s="21" t="inlineStr">
         <is>
           <t>C | 546呎 (2房)
-$2064万
-$37,798/呎
-(在售)</t>
+$1692万
+$30,995/呎
+(26年-09月-14日)</t>
         </is>
       </c>
       <c r="E19" s="22" t="inlineStr">

--- a/web/files/港岛-香港仔及鸭脷洲-海盈山第4B期.xlsx
+++ b/web/files/港岛-香港仔及鸭脷洲-海盈山第4B期.xlsx
@@ -2980,7 +2980,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="H36" s="5" t="n">
@@ -10358,7 +10358,7 @@
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H147" s="5" t="n">
@@ -10668,7 +10668,7 @@
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H152" s="5" t="n">
@@ -11536,7 +11536,7 @@
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H166" s="5" t="n">
@@ -25945,7 +25945,7 @@
           <t>A | 1515呎 (4+房)
 $6984万
 $46,097/呎
-(26年-08月-21日)</t>
+(26年-09月-17日)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -27172,7 +27172,7 @@
           <t>A | 960呎 (3房)
 $4080万
 $42,499/呎
-(26年-08月-21日)</t>
+(26年-09月-16日)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -27219,7 +27219,7 @@
           <t>A | 960呎 (3房)
 $4052万
 $42,203/呎
-(26年-08月-21日)</t>
+(26年-09月-15日)</t>
         </is>
       </c>
       <c r="C21" s="21" t="inlineStr">
@@ -27368,7 +27368,7 @@
           <t>B | 960呎 (3房)
 $3839万
 $39,991/呎
-(26年-08月-24日)</t>
+(26年-09月-15日)</t>
         </is>
       </c>
       <c r="D24" s="21" t="inlineStr">

--- a/web/files/港岛-香港仔及鸭脷洲-海盈山第4B期.xlsx
+++ b/web/files/港岛-香港仔及鸭脷洲-海盈山第4B期.xlsx
@@ -1889,38 +1889,30 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H19" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I19" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="n">
+        <v>61870000</v>
+      </c>
+      <c r="I19" s="5" t="n">
+        <v>51387</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K19" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L19" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K19" s="5" t="n">
+        <v>61870000</v>
+      </c>
+      <c r="L19" s="5" t="n">
+        <v>51387</v>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
@@ -1929,7 +1921,7 @@
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -10606,7 +10598,7 @@
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H151" s="5" t="n">
@@ -25525,7 +25517,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -25535,7 +25527,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -25764,12 +25756,12 @@
 (26年-09月-10日)</t>
         </is>
       </c>
-      <c r="C13" s="22" t="inlineStr">
+      <c r="C13" s="21" t="inlineStr">
         <is>
           <t>B | 1204呎 (4+房)
-招标单位
--
-(在售)</t>
+$6187万
+$51,387/呎
+(26年-09月-18日)</t>
         </is>
       </c>
     </row>
@@ -27227,7 +27219,7 @@
           <t>B | 960呎 (3房)
 $4019万
 $41,868/呎
-(26年-08月-26日)</t>
+(26年-09月-21日)</t>
         </is>
       </c>
       <c r="D21" s="21" t="inlineStr">

--- a/web/files/港岛-香港仔及鸭脷洲-海盈山第4B期.xlsx
+++ b/web/files/港岛-香港仔及鸭脷洲-海盈山第4B期.xlsx
@@ -3537,7 +3537,7 @@
         </is>
       </c>
       <c r="E45" s="4" t="n">
-        <v>1204</v>
+        <v>1154</v>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
@@ -3546,14 +3546,14 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="H45" s="5" t="n">
         <v>50472000</v>
       </c>
       <c r="I45" s="5" t="n">
-        <v>41920</v>
+        <v>43737</v>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
@@ -3564,7 +3564,7 @@
         <v>50472000</v>
       </c>
       <c r="L45" s="5" t="n">
-        <v>41920</v>
+        <v>43737</v>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
@@ -9507,34 +9507,34 @@
       </c>
       <c r="F134" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="H134" s="5" t="n">
-        <v>18195100</v>
+        <v>14920000</v>
       </c>
       <c r="I134" s="5" t="n">
-        <v>37593</v>
+        <v>30826</v>
       </c>
       <c r="J134" s="3" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K134" s="5" t="n">
-        <v>14919982</v>
+        <v>14920000</v>
       </c>
       <c r="L134" s="5" t="n">
         <v>30826</v>
       </c>
       <c r="M134" s="3" t="inlineStr">
         <is>
-          <t>星級 90 天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N134" s="3" t="inlineStr">
@@ -9569,34 +9569,34 @@
       </c>
       <c r="F135" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="H135" s="5" t="n">
-        <v>20637800</v>
+        <v>16923000</v>
       </c>
       <c r="I135" s="5" t="n">
-        <v>37798</v>
+        <v>30995</v>
       </c>
       <c r="J135" s="3" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K135" s="5" t="n">
-        <v>16922996</v>
+        <v>16923000</v>
       </c>
       <c r="L135" s="5" t="n">
-        <v>30994</v>
+        <v>30995</v>
       </c>
       <c r="M135" s="3" t="inlineStr">
         <is>
-          <t>星級 90 天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N135" s="3" t="inlineStr">
@@ -11962,7 +11962,7 @@
       </c>
       <c r="G173" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="H173" s="5" t="n">
@@ -26057,10 +26057,10 @@
       </c>
       <c r="C26" s="21" t="inlineStr">
         <is>
-          <t>B | 1204呎 (4+房)
+          <t>B | 1154呎 (4+房)
 $5047万
-$41,920/呎
-(26年-09月-04日)</t>
+$43,737/呎
+(26年-09月-23日)</t>
         </is>
       </c>
     </row>
@@ -26413,7 +26413,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -26423,7 +26423,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>80</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -27081,15 +27081,62 @@
 (26年-06月-08日)</t>
         </is>
       </c>
-      <c r="D18" s="22" t="inlineStr">
+      <c r="D18" s="21" t="inlineStr">
         <is>
           <t>C | 546呎 (2房)
-$2064万
-$37,798/呎
+$1692万
+$30,995/呎
+(26年-09月-24日)</t>
+        </is>
+      </c>
+      <c r="E18" s="21" t="inlineStr">
+        <is>
+          <t>D | 484呎 (2房)
+$1492万
+$30,826/呎
+(26年-09月-24日)</t>
+        </is>
+      </c>
+      <c r="F18" s="22" t="inlineStr">
+        <is>
+          <t>E | 499呎 (2房)
+$1862万
+$37,321/呎
 (在售)</t>
         </is>
       </c>
-      <c r="E18" s="22" t="inlineStr">
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B19" s="21" t="inlineStr">
+        <is>
+          <t>A | 960呎 (3房)
+$3941万
+$41,055/呎
+(26年-06月-03日)</t>
+        </is>
+      </c>
+      <c r="C19" s="21" t="inlineStr">
+        <is>
+          <t>B | 960呎 (3房)
+$3906万
+$40,691/呎
+(26年-07月-23日)</t>
+        </is>
+      </c>
+      <c r="D19" s="21" t="inlineStr">
+        <is>
+          <t>C | 546呎 (2房)
+$1692万
+$30,995/呎
+(26年-09月-14日)</t>
+        </is>
+      </c>
+      <c r="E19" s="22" t="inlineStr">
         <is>
           <t>D | 484呎 (2房)
 $1820万
@@ -27097,7 +27144,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="F18" s="22" t="inlineStr">
+      <c r="F19" s="22" t="inlineStr">
         <is>
           <t>E | 499呎 (2房)
 $1862万
@@ -27106,53 +27153,6 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="58" customHeight="1">
-      <c r="A19" s="19" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="B19" s="21" t="inlineStr">
-        <is>
-          <t>A | 960呎 (3房)
-$3941万
-$41,055/呎
-(26年-06月-03日)</t>
-        </is>
-      </c>
-      <c r="C19" s="21" t="inlineStr">
-        <is>
-          <t>B | 960呎 (3房)
-$3906万
-$40,691/呎
-(26年-07月-23日)</t>
-        </is>
-      </c>
-      <c r="D19" s="21" t="inlineStr">
-        <is>
-          <t>C | 546呎 (2房)
-$1692万
-$30,995/呎
-(26年-09月-14日)</t>
-        </is>
-      </c>
-      <c r="E19" s="22" t="inlineStr">
-        <is>
-          <t>D | 484呎 (2房)
-$1820万
-$37,593/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F19" s="22" t="inlineStr">
-        <is>
-          <t>E | 499呎 (2房)
-$1862万
-$37,321/呎
-(在售)</t>
-        </is>
-      </c>
-    </row>
     <row r="20" ht="58" customHeight="1">
       <c r="A20" s="19" t="inlineStr">
         <is>
@@ -27478,7 +27478,7 @@
           <t>E | 499呎 (2房)
 $1436万
 $28,780/呎
-(26年-09月-08日)</t>
+(26年-09月-24日)</t>
         </is>
       </c>
     </row>

--- a/web/files/港岛-香港仔及鸭脷洲-海盈山第4B期.xlsx
+++ b/web/files/港岛-香港仔及鸭脷洲-海盈山第4B期.xlsx
@@ -2336,7 +2336,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H26" s="5" t="n">
@@ -2840,7 +2840,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H34" s="5" t="n">
@@ -12272,7 +12272,7 @@
       </c>
       <c r="G178" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="H178" s="5" t="n">
@@ -14056,7 +14056,7 @@
       </c>
       <c r="G206" s="3" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="H206" s="5" t="n">
@@ -25822,7 +25822,7 @@
           <t>A | 1515呎 (4+房)
 $7540万
 $49,766/呎
-(26年-09月-11日)</t>
+(26年-09月-28日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -25914,7 +25914,7 @@
           <t>A | 1515呎 (4+房)
 $7346万
 $48,491/呎
-(26年-09月-09日)</t>
+(26年-09月-28日)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -27525,7 +27525,7 @@
           <t>E | 499呎 (2房)
 $1430万
 $28,665/呎
-(26年-09月-10日)</t>
+(26年-09月-25日)</t>
         </is>
       </c>
     </row>
@@ -27736,7 +27736,7 @@
           <t>B | 960呎 (3房)
 $3380万
 $35,208/呎
-(26年-08月-26日)</t>
+(26年-09月-28日)</t>
         </is>
       </c>
       <c r="D32" s="21" t="inlineStr">

--- a/web/files/港岛-香港仔及鸭脷洲-海盈山第4B期.xlsx
+++ b/web/files/港岛-香港仔及鸭脷洲-海盈山第4B期.xlsx
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="E55" s="4" t="n">
-        <v>1204</v>
+        <v>1154</v>
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
@@ -4198,14 +4198,14 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="H55" s="5" t="n">
         <v>48118000</v>
       </c>
       <c r="I55" s="5" t="n">
-        <v>39965</v>
+        <v>41697</v>
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
@@ -4216,7 +4216,7 @@
         <v>48118000</v>
       </c>
       <c r="L55" s="5" t="n">
-        <v>39965</v>
+        <v>41697</v>
       </c>
       <c r="M55" s="3" t="inlineStr">
         <is>
@@ -10275,38 +10275,30 @@
       </c>
       <c r="F146" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H146" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I146" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="H146" s="5" t="n">
+        <v>40474000</v>
+      </c>
+      <c r="I146" s="5" t="n">
+        <v>42160</v>
       </c>
       <c r="J146" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K146" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L146" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K146" s="5" t="n">
+        <v>40474000</v>
+      </c>
+      <c r="L146" s="5" t="n">
+        <v>42160</v>
       </c>
       <c r="M146" s="3" t="inlineStr">
         <is>
@@ -10315,7 +10307,7 @@
       </c>
       <c r="N146" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -12024,7 +12016,7 @@
       </c>
       <c r="G174" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H174" s="5" t="n">
@@ -13870,7 +13862,7 @@
       </c>
       <c r="G203" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="H203" s="5" t="n">
@@ -26172,10 +26164,10 @@
       </c>
       <c r="C31" s="21" t="inlineStr">
         <is>
-          <t>B | 1204呎 (4+房)
+          <t>B | 1154呎 (4+房)
 $4812万
-$39,965/呎
-(26年-09月-11日)</t>
+$41,697/呎
+(26年-10月-02日)</t>
         </is>
       </c>
     </row>
@@ -26413,7 +26405,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -26423,7 +26415,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>81</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -27167,12 +27159,12 @@
 (26年-09月-16日)</t>
         </is>
       </c>
-      <c r="C20" s="22" t="inlineStr">
+      <c r="C20" s="21" t="inlineStr">
         <is>
           <t>B | 960呎 (3房)
-招标单位
--
-(在售)</t>
+$4047万
+$42,160/呎
+(26年-09月-30日)</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -27470,7 +27462,7 @@
           <t>D | 484呎 (2房)
 $1403万
 $28,988/呎
-(26年-09月-06日)</t>
+(26年-09月-30日)</t>
         </is>
       </c>
       <c r="F26" s="21" t="inlineStr">
@@ -27760,7 +27752,7 @@
           <t>E | 499呎 (2房)
 $1402万
 $28,100/呎
-(26年-09月-05日)</t>
+(26年-10月-02日)</t>
         </is>
       </c>
     </row>

--- a/web/files/港岛-香港仔及鸭脷洲-海盈山第4B期.xlsx
+++ b/web/files/港岛-香港仔及鸭脷洲-海盈山第4B期.xlsx
@@ -1885,7 +1885,7 @@
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>1204</v>
+        <v>1154</v>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
@@ -1894,14 +1894,14 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="H19" s="5" t="n">
         <v>61870000</v>
       </c>
       <c r="I19" s="5" t="n">
-        <v>51387</v>
+        <v>53614</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
@@ -1912,7 +1912,7 @@
         <v>61870000</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>51387</v>
+        <v>53614</v>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
@@ -25750,10 +25750,10 @@
       </c>
       <c r="C13" s="21" t="inlineStr">
         <is>
-          <t>B | 1204呎 (4+房)
+          <t>B | 1154呎 (4+房)
 $6187万
-$51,387/呎
-(26年-09月-18日)</t>
+$53,614/呎
+(26年-10月-07日)</t>
         </is>
       </c>
     </row>

--- a/web/files/港岛-香港仔及鸭脷洲-海盈山第4B期.xlsx
+++ b/web/files/港岛-香港仔及鸭脷洲-海盈山第4B期.xlsx
@@ -9884,7 +9884,7 @@
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="H140" s="5" t="n">
@@ -27125,7 +27125,7 @@
           <t>C | 546呎 (2房)
 $1692万
 $30,995/呎
-(26年-09月-14日)</t>
+(26年-10月-12日)</t>
         </is>
       </c>
       <c r="E19" s="22" t="inlineStr">

--- a/web/files/港岛-香港仔及鸭脷洲-海盈山第4B期.xlsx
+++ b/web/files/港岛-香港仔及鸭脷洲-海盈山第4B期.xlsx
@@ -9512,7 +9512,7 @@
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H134" s="5" t="n">
@@ -9574,7 +9574,7 @@
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H135" s="5" t="n">
@@ -10280,7 +10280,7 @@
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H146" s="5" t="n">
@@ -10399,34 +10399,34 @@
       </c>
       <c r="F148" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="H148" s="5" t="n">
-        <v>17867000</v>
+        <v>14651000</v>
       </c>
       <c r="I148" s="5" t="n">
-        <v>35806</v>
+        <v>29361</v>
       </c>
       <c r="J148" s="3" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K148" s="5" t="n">
-        <v>14650940</v>
+        <v>14651000</v>
       </c>
       <c r="L148" s="5" t="n">
         <v>29361</v>
       </c>
       <c r="M148" s="3" t="inlineStr">
         <is>
-          <t>星級 90 天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N148" s="3" t="inlineStr">
@@ -26405,7 +26405,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -26415,7 +26415,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>82</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -27078,7 +27078,7 @@
           <t>C | 546呎 (2房)
 $1692万
 $30,995/呎
-(26年-09月-24日)</t>
+(26年-10月-20日)</t>
         </is>
       </c>
       <c r="E18" s="21" t="inlineStr">
@@ -27086,7 +27086,7 @@
           <t>D | 484呎 (2房)
 $1492万
 $30,826/呎
-(26年-09月-24日)</t>
+(26年-10月-20日)</t>
         </is>
       </c>
       <c r="F18" s="22" t="inlineStr">
@@ -27164,7 +27164,7 @@
           <t>B | 960呎 (3房)
 $4047万
 $42,160/呎
-(26年-09月-30日)</t>
+(26年-10月-20日)</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -27230,12 +27230,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="F21" s="22" t="inlineStr">
+      <c r="F21" s="21" t="inlineStr">
         <is>
           <t>E | 499呎 (2房)
-$1787万
-$35,806/呎
-(在售)</t>
+$1465万
+$29,361/呎
+(26年-10月-25日)</t>
         </is>
       </c>
     </row>

--- a/web/files/港岛-香港仔及鸭脷洲-海盈山第4B期.xlsx
+++ b/web/files/港岛-香港仔及鸭脷洲-海盈山第4B期.xlsx
@@ -1885,7 +1885,7 @@
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>1154</v>
+        <v>1204</v>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
         <v>61870000</v>
       </c>
       <c r="I19" s="5" t="n">
-        <v>53614</v>
+        <v>51387</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
@@ -1912,7 +1912,7 @@
         <v>61870000</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>53614</v>
+        <v>51387</v>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="E21" s="4" t="n">
-        <v>1154</v>
+        <v>1204</v>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
         <v>56252000</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>48745</v>
+        <v>46721</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>56252000</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>48745</v>
+        <v>46721</v>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         </is>
       </c>
       <c r="E23" s="4" t="n">
-        <v>1154</v>
+        <v>1204</v>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>56252000</v>
       </c>
       <c r="I23" s="5" t="n">
-        <v>48745</v>
+        <v>46721</v>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
@@ -2160,7 +2160,7 @@
         <v>56252000</v>
       </c>
       <c r="L23" s="5" t="n">
-        <v>48745</v>
+        <v>46721</v>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
@@ -2389,7 +2389,7 @@
         </is>
       </c>
       <c r="E27" s="4" t="n">
-        <v>1154</v>
+        <v>1204</v>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
@@ -2405,7 +2405,7 @@
         <v>53722000</v>
       </c>
       <c r="I27" s="5" t="n">
-        <v>46553</v>
+        <v>44620</v>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
@@ -2416,7 +2416,7 @@
         <v>53722000</v>
       </c>
       <c r="L27" s="5" t="n">
-        <v>46553</v>
+        <v>44620</v>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
@@ -2513,7 +2513,7 @@
         </is>
       </c>
       <c r="E29" s="4" t="n">
-        <v>1154</v>
+        <v>1204</v>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
@@ -2529,7 +2529,7 @@
         <v>53350444</v>
       </c>
       <c r="I29" s="5" t="n">
-        <v>46231</v>
+        <v>44311</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
@@ -2540,7 +2540,7 @@
         <v>53350444</v>
       </c>
       <c r="L29" s="5" t="n">
-        <v>46231</v>
+        <v>44311</v>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="E31" s="4" t="n">
-        <v>1154</v>
+        <v>1204</v>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
@@ -2653,7 +2653,7 @@
         <v>53350000</v>
       </c>
       <c r="I31" s="5" t="n">
-        <v>46231</v>
+        <v>44311</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
@@ -2664,7 +2664,7 @@
         <v>53350000</v>
       </c>
       <c r="L31" s="5" t="n">
-        <v>46231</v>
+        <v>44311</v>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
@@ -3025,7 +3025,7 @@
         </is>
       </c>
       <c r="E37" s="4" t="n">
-        <v>1154</v>
+        <v>1204</v>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
@@ -3041,7 +3041,7 @@
         <v>51892000</v>
       </c>
       <c r="I37" s="5" t="n">
-        <v>44967</v>
+        <v>43100</v>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
@@ -3052,7 +3052,7 @@
         <v>51892000</v>
       </c>
       <c r="L37" s="5" t="n">
-        <v>44967</v>
+        <v>43100</v>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
@@ -3343,7 +3343,7 @@
         </is>
       </c>
       <c r="E42" s="4" t="n">
-        <v>1450</v>
+        <v>1515</v>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         <v>69553000</v>
       </c>
       <c r="I42" s="5" t="n">
-        <v>47968</v>
+        <v>45910</v>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
@@ -3370,7 +3370,7 @@
         <v>69553000</v>
       </c>
       <c r="L42" s="5" t="n">
-        <v>47968</v>
+        <v>45910</v>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
@@ -3475,7 +3475,7 @@
         </is>
       </c>
       <c r="E44" s="4" t="n">
-        <v>1450</v>
+        <v>1515</v>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
@@ -3491,7 +3491,7 @@
         <v>66306000</v>
       </c>
       <c r="I44" s="5" t="n">
-        <v>45728</v>
+        <v>43766</v>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
@@ -3502,7 +3502,7 @@
         <v>66306000</v>
       </c>
       <c r="L44" s="5" t="n">
-        <v>45728</v>
+        <v>43766</v>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
@@ -3537,7 +3537,7 @@
         </is>
       </c>
       <c r="E45" s="4" t="n">
-        <v>1154</v>
+        <v>1204</v>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
@@ -3553,7 +3553,7 @@
         <v>50472000</v>
       </c>
       <c r="I45" s="5" t="n">
-        <v>43737</v>
+        <v>41920</v>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
@@ -3564,7 +3564,7 @@
         <v>50472000</v>
       </c>
       <c r="L45" s="5" t="n">
-        <v>43737</v>
+        <v>41920</v>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
@@ -3599,7 +3599,7 @@
         </is>
       </c>
       <c r="E46" s="4" t="n">
-        <v>1450</v>
+        <v>1515</v>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
         <v>64187000</v>
       </c>
       <c r="I46" s="5" t="n">
-        <v>44267</v>
+        <v>42368</v>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
@@ -3626,7 +3626,7 @@
         <v>64187000</v>
       </c>
       <c r="L46" s="5" t="n">
-        <v>44267</v>
+        <v>42368</v>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
@@ -3661,7 +3661,7 @@
         </is>
       </c>
       <c r="E47" s="4" t="n">
-        <v>1154</v>
+        <v>1204</v>
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
@@ -3677,7 +3677,7 @@
         <v>50123000</v>
       </c>
       <c r="I47" s="5" t="n">
-        <v>43434</v>
+        <v>41630</v>
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
@@ -3688,7 +3688,7 @@
         <v>50123000</v>
       </c>
       <c r="L47" s="5" t="n">
-        <v>43434</v>
+        <v>41630</v>
       </c>
       <c r="M47" s="3" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="E49" s="4" t="n">
-        <v>1154</v>
+        <v>1204</v>
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
@@ -3801,7 +3801,7 @@
         <v>49777000</v>
       </c>
       <c r="I49" s="5" t="n">
-        <v>43134</v>
+        <v>41343</v>
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
@@ -3812,7 +3812,7 @@
         <v>49777000</v>
       </c>
       <c r="L49" s="5" t="n">
-        <v>43134</v>
+        <v>41343</v>
       </c>
       <c r="M49" s="3" t="inlineStr">
         <is>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="E55" s="4" t="n">
-        <v>1154</v>
+        <v>1204</v>
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
@@ -4205,7 +4205,7 @@
         <v>48118000</v>
       </c>
       <c r="I55" s="5" t="n">
-        <v>41697</v>
+        <v>39965</v>
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
@@ -4216,7 +4216,7 @@
         <v>48118000</v>
       </c>
       <c r="L55" s="5" t="n">
-        <v>41697</v>
+        <v>39965</v>
       </c>
       <c r="M55" s="3" t="inlineStr">
         <is>
@@ -14105,38 +14105,30 @@
       </c>
       <c r="F207" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G207" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H207" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I207" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="H207" s="5" t="n">
+        <v>34517000</v>
+      </c>
+      <c r="I207" s="5" t="n">
+        <v>35955</v>
       </c>
       <c r="J207" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K207" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L207" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K207" s="5" t="n">
+        <v>34517000</v>
+      </c>
+      <c r="L207" s="5" t="n">
+        <v>35955</v>
       </c>
       <c r="M207" s="3" t="inlineStr">
         <is>
@@ -14145,7 +14137,7 @@
       </c>
       <c r="N207" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -25750,9 +25742,9 @@
       </c>
       <c r="C13" s="21" t="inlineStr">
         <is>
-          <t>B | 1154呎 (4+房)
+          <t>B | 1204呎 (4+房)
 $6187万
-$53,614/呎
+$51,387/呎
 (26年-10月-07日)</t>
         </is>
       </c>
@@ -25773,9 +25765,9 @@
       </c>
       <c r="C14" s="21" t="inlineStr">
         <is>
-          <t>B | 1154呎 (4+房)
+          <t>B | 1204呎 (4+房)
 $5625万
-$48,745/呎
+$46,721/呎
 (26年-06月-09日)</t>
         </is>
       </c>
@@ -25796,9 +25788,9 @@
       </c>
       <c r="C15" s="21" t="inlineStr">
         <is>
-          <t>B | 1154呎 (4+房)
+          <t>B | 1204呎 (4+房)
 $5625万
-$48,745/呎
+$46,721/呎
 (26年-06月-25日)</t>
         </is>
       </c>
@@ -25842,9 +25834,9 @@
       </c>
       <c r="C17" s="21" t="inlineStr">
         <is>
-          <t>B | 1154呎 (4+房)
+          <t>B | 1204呎 (4+房)
 $5372万
-$46,553/呎
+$44,620/呎
 (26年-06月-11日)</t>
         </is>
       </c>
@@ -25865,9 +25857,9 @@
       </c>
       <c r="C18" s="21" t="inlineStr">
         <is>
-          <t>B | 1154呎 (4+房)
+          <t>B | 1204呎 (4+房)
 $5335万
-$46,231/呎
+$44,311/呎
 (26年-06月-08日)</t>
         </is>
       </c>
@@ -25888,9 +25880,9 @@
       </c>
       <c r="C19" s="21" t="inlineStr">
         <is>
-          <t>B | 1154呎 (4+房)
+          <t>B | 1204呎 (4+房)
 $5335万
-$46,231/呎
+$44,311/呎
 (26年-06月-04日)</t>
         </is>
       </c>
@@ -25957,9 +25949,9 @@
       </c>
       <c r="C22" s="21" t="inlineStr">
         <is>
-          <t>B | 1154呎 (4+房)
+          <t>B | 1204呎 (4+房)
 $5189万
-$44,967/呎
+$43,100/呎
 (26年-06月-05日)</t>
         </is>
       </c>
@@ -25995,9 +25987,9 @@
       </c>
       <c r="B24" s="21" t="inlineStr">
         <is>
-          <t>A | 1450呎 (4+房)
+          <t>A | 1515呎 (4+房)
 $6955万
-$47,968/呎
+$45,910/呎
 (26年-06月-16日)</t>
         </is>
       </c>
@@ -26018,9 +26010,9 @@
       </c>
       <c r="B25" s="21" t="inlineStr">
         <is>
-          <t>A | 1450呎 (4+房)
+          <t>A | 1515呎 (4+房)
 $6631万
-$45,728/呎
+$43,766/呎
 (26年-06月-16日)</t>
         </is>
       </c>
@@ -26041,17 +26033,17 @@
       </c>
       <c r="B26" s="21" t="inlineStr">
         <is>
-          <t>A | 1450呎 (4+房)
+          <t>A | 1515呎 (4+房)
 $6419万
-$44,267/呎
+$42,368/呎
 (26年-06月-15日)</t>
         </is>
       </c>
       <c r="C26" s="21" t="inlineStr">
         <is>
-          <t>B | 1154呎 (4+房)
+          <t>B | 1204呎 (4+房)
 $5047万
-$43,737/呎
+$41,920/呎
 (26年-09月-23日)</t>
         </is>
       </c>
@@ -26072,9 +26064,9 @@
       </c>
       <c r="C27" s="21" t="inlineStr">
         <is>
-          <t>B | 1154呎 (4+房)
+          <t>B | 1204呎 (4+房)
 $5012万
-$43,434/呎
+$41,630/呎
 (26年-06月-12日)</t>
         </is>
       </c>
@@ -26095,9 +26087,9 @@
       </c>
       <c r="C28" s="21" t="inlineStr">
         <is>
-          <t>B | 1154呎 (4+房)
+          <t>B | 1204呎 (4+房)
 $4978万
-$43,134/呎
+$41,343/呎
 (26年-06月-23日)</t>
         </is>
       </c>
@@ -26164,9 +26156,9 @@
       </c>
       <c r="C31" s="21" t="inlineStr">
         <is>
-          <t>B | 1154呎 (4+房)
+          <t>B | 1204呎 (4+房)
 $4812万
-$41,697/呎
+$39,965/呎
 (26年-10月-02日)</t>
         </is>
       </c>
@@ -26405,7 +26397,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -26415,7 +26407,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>83</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -27715,12 +27707,12 @@
           <t>11</t>
         </is>
       </c>
-      <c r="B32" s="22" t="inlineStr">
+      <c r="B32" s="21" t="inlineStr">
         <is>
           <t>A | 960呎 (3房)
-招标单位
--
-(在售)</t>
+$3452万
+$35,955/呎
+(26年-10月-28日)</t>
         </is>
       </c>
       <c r="C32" s="21" t="inlineStr">
